--- a/artfynd/A 38164-2026 artfynd.xlsx
+++ b/artfynd/A 38164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136989380</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136985782</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38164-2026 artfynd.xlsx
+++ b/artfynd/A 38164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136989380</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136985782</v>
       </c>
       <c r="B3" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38164-2026 artfynd.xlsx
+++ b/artfynd/A 38164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136989380</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136985782</v>
       </c>
       <c r="B3" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38164-2026 artfynd.xlsx
+++ b/artfynd/A 38164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136989380</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136985782</v>
       </c>
       <c r="B3" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38164-2026 artfynd.xlsx
+++ b/artfynd/A 38164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136989380</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136985782</v>
       </c>
       <c r="B3" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38164-2026 artfynd.xlsx
+++ b/artfynd/A 38164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136989380</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136985782</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
